--- a/docs/Mapping_casi_uso/cittadinanza/Citt_008.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_008.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="138">
   <si>
     <t>Sezione</t>
   </si>
@@ -276,6 +276,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Dati accertamento</t>
@@ -478,11 +484,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.65234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="49.65234375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -1343,19 +1349,19 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>10</v>
@@ -1366,16 +1372,16 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>93</v>
@@ -1389,7 +1395,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>94</v>
@@ -1398,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>95</v>
@@ -1412,7 +1418,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>96</v>
@@ -1421,7 +1427,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>97</v>
@@ -1435,16 +1441,16 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>99</v>
@@ -1458,7 +1464,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>100</v>
@@ -1467,7 +1473,7 @@
         <v>33</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>101</v>
@@ -1481,7 +1487,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>102</v>
@@ -1490,7 +1496,7 @@
         <v>33</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>103</v>
@@ -1504,7 +1510,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>104</v>
@@ -1513,7 +1519,7 @@
         <v>33</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>105</v>
@@ -1527,7 +1533,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>106</v>
@@ -1536,7 +1542,7 @@
         <v>33</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>107</v>
@@ -1550,19 +1556,19 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -1573,16 +1579,16 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>113</v>
@@ -1596,7 +1602,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>114</v>
@@ -1605,7 +1611,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>115</v>
@@ -1619,7 +1625,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>116</v>
@@ -1628,7 +1634,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>117</v>
@@ -1642,7 +1648,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>118</v>
@@ -1651,7 +1657,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>119</v>
@@ -1665,7 +1671,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>120</v>
@@ -1674,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>121</v>
@@ -1688,7 +1694,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>122</v>
@@ -1697,10 +1703,10 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -1711,19 +1717,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1734,19 +1740,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
@@ -1757,19 +1763,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1780,7 +1786,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>128</v>
@@ -1789,7 +1795,7 @@
         <v>33</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>129</v>
@@ -1803,7 +1809,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>130</v>
@@ -1812,7 +1818,7 @@
         <v>33</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>131</v>
@@ -1826,16 +1832,16 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>133</v>
@@ -1849,19 +1855,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="C60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1872,16 +1878,16 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>93</v>
@@ -1895,7 +1901,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>94</v>
@@ -1904,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>95</v>
@@ -1918,19 +1924,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -1941,16 +1947,16 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>103</v>
@@ -1964,16 +1970,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>105</v>
@@ -1987,16 +1993,16 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>107</v>
@@ -2005,6 +2011,29 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>18</v>
       </c>
     </row>
